--- a/business_report_forms/019_weekly_experiment_findings_report_form--business_report_forms.xlsx
+++ b/business_report_forms/019_weekly_experiment_findings_report_form--business_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -750,8 +750,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -779,12 +779,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'positive',_'value':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Positive', 'value': 'positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'negative',_'value':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Negative', 'value': 'negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral',_'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral', 'value': 'neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_1,_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 1, 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_2,_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 2, 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_3,_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 3, 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_4,_'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 4, 'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_5,_'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 5, 'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'team_member_1',_'value':_'team_member_1'}</t>
+          <t>team_member_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Team Member 1', 'value': 'team_member_1'}</t>
+          <t>Team Member 1</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'team_member_2',_'value':_'team_member_2'}</t>
+          <t>team_member_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Team Member 2', 'value': 'team_member_2'}</t>
+          <t>Team Member 2</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'team_member_3',_'value':_'team_member_3'}</t>
+          <t>team_member_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Team Member 3', 'value': 'team_member_3'}</t>
+          <t>Team Member 3</t>
         </is>
       </c>
     </row>
